--- a/output/2026-10-06_03_Croazia_Grad_Zagreb_Cleaning.xlsx
+++ b/output/2026-10-06_03_Croazia_Grad_Zagreb_Cleaning.xlsx
@@ -494,10 +494,9 @@
           <t>+385 1 3818 004</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Premium Partner certificato Filtration Group Industrial per filtrazione aria/aspirazione polveri industriali. Attivita' principale meccatronica/pneumatica/idraulica; linea air-filtration confermata anche su industrial.filtrationgroup.com. Email non riportata: risultati mostravano solo indirizzi mascherati.</t>
+          <t>Premium Partner certificato Filtration Group Industrial per filtrazione aria/aspirazione polveri industriali. Attivita' principale meccatronica/pneumatica/idraulica; linea air-filtration confermata anche su industrial.filtrationgroup.com. Email non riportata: risultati mostravano solo indirizzi mascherati. [DUPLICATO — vedi anche: 2026-10-05_20_Croazia_Međimurska_Impiantistica_aspirazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -581,7 +580,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Progettazione/produzione/vendita sistemi di aspirazione-filtrazione industriale polveri (dust collector) e cabine di verniciatura. ATTENZIONE: ruolo di produttore/system integrator piu' che semplice distributore/rivenditore multimarca; da validare commercialmente come partner tecnico.</t>
+          <t>Progettazione/produzione/vendita sistemi di aspirazione-filtrazione industriale polveri (dust collector) e cabine di verniciatura. ATTENZIONE: ruolo di produttore/system integrator piu' che semplice distributore/rivenditore multimarca; da validare commercialmente come partner tecnico. [DUPLICATO — vedi anche: 2026-09-13_02_Croazia_Varazdinska_ATEX_Equipment-Services.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">

--- a/output/2026-10-06_03_Croazia_Grad_Zagreb_Cleaning.xlsx
+++ b/output/2026-10-06_03_Croazia_Grad_Zagreb_Cleaning.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
